--- a/数据目录.xlsx
+++ b/数据目录.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2-项目代码\data_tool\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2-项目代码\aistockzml\data_tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972D8788-D3D4-44B7-B95D-24128FD952B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BFFB1D4-16A1-41C7-A3A7-9515A1A16563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22365" yWindow="0" windowWidth="22905" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="源数据" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="168">
   <si>
     <t>表英文名</t>
   </si>
@@ -394,6 +394,234 @@
   </si>
   <si>
     <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tushare.pro/document/2?doc_id=170</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资金流向</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moneyflow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>个股资金流向</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aistockzml_tushare_moneyflow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>个股资金流向（THS）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moneyflow_ths</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tushare.pro/document/2?doc_id=348</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aistockzml_tushare_moneyflow_ths</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tushare.pro/document/2?doc_id=349</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moneyflow_dc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>个股资金流向（DC）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aistockzml_tushare_moneyflow_dc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tushare.pro/document/2?doc_id=371</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moneyflow_cnt_ths</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同花顺概念板块资金流向（THS）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aistockzml_tushare_moneyflow_cnt_ths</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同花顺行业资金流向（THS）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moneyflow_ind_ths</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tushare.pro/document/2?doc_id=343</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aistockzml_tushare_moneyflow_ind_ths</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moneyflow_ind_dc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tushare.pro/document/2?doc_id=344</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>东财概念及行业板块资金流向（DC）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aistockzml_tushare_moneyflow_ind_dc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大盘资金流向（DC）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tushare.pro/document/2?doc_id=345</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moneyflow_mkt_dc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aistockzml_tushare_moneyflow_mkt_dc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moneyflow_hsgt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沪深港通资金流向</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tushare.pro/document/2?doc_id=47</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aistockzml_tushare_moneyflow_hsgt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以接口形式调用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tushare.pro/document/2?doc_id=110</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>股权质押统计数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pledge_stat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参考数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>股权质押明细</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pledge_detail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tushare.pro/document/2?doc_id=111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>股票回购</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>repurchase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tushare.pro/document/2?doc_id=124</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aistockzml_tushare_repurchase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tushare.pro/document/2?doc_id=161</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>block_trade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大宗交易</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aistockzml_tushare_block_trade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>股东人数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stk_holdernumber</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tushare.pro/document/2?doc_id=166</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aistockzml_tushare_stk_holdernumber</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aistockzml_tushare_stk_holdertrade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stk_holdertrade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>股东增减持</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tushare.pro/document/2?doc_id=175</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -401,7 +629,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -417,23 +645,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -441,8 +652,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -452,6 +686,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -467,20 +707,30 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -785,19 +1035,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:G47"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.375" customWidth="1"/>
-    <col min="2" max="2" width="39.875" customWidth="1"/>
-    <col min="3" max="3" width="31.25" customWidth="1"/>
-    <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="5" width="17.25" customWidth="1"/>
-    <col min="6" max="6" width="13.125" customWidth="1"/>
-    <col min="7" max="7" width="42" customWidth="1"/>
+    <col min="1" max="1" width="7.375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="39.875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="31.25" style="4" customWidth="1"/>
+    <col min="4" max="4" width="27" style="4" customWidth="1"/>
+    <col min="5" max="5" width="17.25" style="4" customWidth="1"/>
+    <col min="6" max="6" width="13.125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="42" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -820,606 +1071,976 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A2" s="1">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="F2" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G2" s="7" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A3" s="1">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A4" s="1">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G4" s="4" t="s">
+      <c r="F4" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A5" s="1">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="F5" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A6" s="1">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="F6" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A7" s="1">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="F7" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A8" s="1">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="F8" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A9" s="1">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="F9" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A10" s="1">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="F10" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A11" s="1">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="F11" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A12" s="1">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G12" s="4" t="s">
+      <c r="F12" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A13" s="1">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G13" s="4" t="s">
+      <c r="F13" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A14" s="1">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G14" s="4" t="s">
+      <c r="F14" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A15" s="1">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G15" s="4" t="s">
+      <c r="F15" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A16" s="1">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G16" s="4" t="s">
+      <c r="F16" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A17" s="1">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G17" s="4" t="s">
+      <c r="F17" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A18" s="1">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G18" s="4" t="s">
+      <c r="F18" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G18" s="7" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A19" s="1">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G19" s="4" t="s">
+      <c r="F19" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A20" s="1">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G20" s="4" t="s">
+      <c r="F20" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A21" s="1">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="F21" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G21" s="7" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A22" s="1">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="F22" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G22" s="7" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A23" s="1">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G23" s="4" t="s">
+      <c r="F23" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" s="7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A24" s="1">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F24" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G24" s="4" t="s">
+      <c r="F24" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A25" s="1">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F25" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G25" s="4" t="s">
+      <c r="F25" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G25" s="7" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A26" s="1">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="5">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F26" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G26" s="4" t="s">
+      <c r="F26" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" s="7" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A27" s="1">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="5">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F27" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G27" s="4" t="s">
+      <c r="F27" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G27" s="7" t="s">
         <v>108</v>
       </c>
     </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="5">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="5">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="5">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="5">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="5">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="5">
+        <v>32</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="5">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="5">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="5">
+        <v>34</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="5">
+        <v>34</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="5">
+        <v>34</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="5">
+        <v>34</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="5"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="7"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="5"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="7"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C45" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C46" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G47" s="1"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A43:G43"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="G28" r:id="rId1" xr:uid="{864D94FA-F83F-4A5C-A41B-D3B55D949D28}"/>
+    <hyperlink ref="G29" r:id="rId2" xr:uid="{3CB1C400-10E5-4CAC-8396-4ECAC51BA654}"/>
+    <hyperlink ref="G30" r:id="rId3" xr:uid="{294DCEE3-7771-47EF-99AB-E681ED52FAB0}"/>
+    <hyperlink ref="G31" r:id="rId4" xr:uid="{01A2ED62-C9D1-4956-870A-2F59AC77A2F1}"/>
+    <hyperlink ref="G32" r:id="rId5" xr:uid="{2603B890-7AC9-4FF3-B8CC-04925B6F3A32}"/>
+    <hyperlink ref="G33" r:id="rId6" xr:uid="{E6A59528-F97C-48F8-9E05-9FD9696787F4}"/>
+    <hyperlink ref="G34" r:id="rId7" xr:uid="{FF07FB43-ED15-44D7-9023-E5619BD25FBD}"/>
+    <hyperlink ref="G35" r:id="rId8" xr:uid="{A3A2AB3A-90C2-4ADA-8FE9-73F3591C8D75}"/>
+    <hyperlink ref="G45" r:id="rId9" xr:uid="{603F17D4-9075-4A51-AE9A-CF321AC925FE}"/>
+    <hyperlink ref="G46" r:id="rId10" xr:uid="{909D3289-9B93-4C29-B575-ACDF08F6BDA0}"/>
+    <hyperlink ref="G36" r:id="rId11" xr:uid="{C3E5FB04-ECE0-406E-859B-EBE9F0D89022}"/>
+    <hyperlink ref="G37" r:id="rId12" xr:uid="{831D7BB0-4B70-4932-AE66-10794C9F541D}"/>
+    <hyperlink ref="G38" r:id="rId13" xr:uid="{74C8848E-5826-48FB-994F-8A09DFBDADFD}"/>
+    <hyperlink ref="G39" r:id="rId14" xr:uid="{542CB839-9090-400F-86DC-D1AD09F695B5}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/数据目录.xlsx
+++ b/数据目录.xlsx
@@ -5,22 +5,26 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2-项目代码\aistockzml\data_tools\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2-项目代码\aistockzml\data_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{086A3E85-5DDE-41EB-AA21-7BC72B61A86D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{A1FE921F-1306-4111-97C0-176202B0A382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15105" yWindow="0" windowWidth="33735" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="源数据" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">源数据!$A$1:$L$39</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="182">
   <si>
     <t>表英文名</t>
   </si>
@@ -667,6 +671,25 @@
   </si>
   <si>
     <t>ts_financial_report_task.py</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ts_stock_basic_task.py</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ts_stock_quotes_task.py</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ts_stock_moneyflow_task.py</t>
+  </si>
+  <si>
+    <t>ts_stock_others_task.py</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -735,7 +758,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -760,6 +783,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -774,7 +803,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -797,10 +826,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -810,15 +835,26 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1122,6 +1158,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:L47"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1384,33 +1421,33 @@
         <v>162</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="16">
+    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="14">
         <v>7</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17" t="s">
+      <c r="E8" s="15"/>
+      <c r="F8" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="G8" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="H8" s="19" t="s">
+      <c r="G8" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="H8" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="20" t="s">
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="18" t="s">
         <v>169</v>
       </c>
     </row>
@@ -1462,6 +1499,9 @@
       <c r="D10" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="E10" s="4" t="s">
+        <v>176</v>
+      </c>
       <c r="F10" s="4" t="s">
         <v>6</v>
       </c>
@@ -1471,9 +1511,15 @@
       <c r="H10" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
+      <c r="I10" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
@@ -1488,6 +1534,9 @@
       <c r="D11" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="E11" s="4" t="s">
+        <v>177</v>
+      </c>
       <c r="F11" s="4" t="s">
         <v>26</v>
       </c>
@@ -1497,9 +1546,15 @@
       <c r="H11" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
+      <c r="I11" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
@@ -1514,6 +1569,9 @@
       <c r="D12" s="4" t="s">
         <v>28</v>
       </c>
+      <c r="E12" s="4" t="s">
+        <v>177</v>
+      </c>
       <c r="F12" s="4" t="s">
         <v>26</v>
       </c>
@@ -1523,9 +1581,15 @@
       <c r="H12" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
+      <c r="I12" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
@@ -1540,6 +1604,9 @@
       <c r="D13" s="4" t="s">
         <v>30</v>
       </c>
+      <c r="E13" s="4" t="s">
+        <v>177</v>
+      </c>
       <c r="F13" s="4" t="s">
         <v>26</v>
       </c>
@@ -1549,9 +1616,15 @@
       <c r="H13" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
+      <c r="I13" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
@@ -1566,6 +1639,9 @@
       <c r="D14" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="E14" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="F14" s="4" t="s">
         <v>33</v>
       </c>
@@ -1575,9 +1651,15 @@
       <c r="H14" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
+      <c r="I14" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
@@ -1592,6 +1674,9 @@
       <c r="D15" s="4" t="s">
         <v>36</v>
       </c>
+      <c r="E15" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="F15" s="4" t="s">
         <v>33</v>
       </c>
@@ -1601,9 +1686,15 @@
       <c r="H15" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
+      <c r="I15" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
@@ -1618,6 +1709,9 @@
       <c r="D16" s="4" t="s">
         <v>39</v>
       </c>
+      <c r="E16" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="F16" s="4" t="s">
         <v>33</v>
       </c>
@@ -1627,9 +1721,15 @@
       <c r="H16" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
+      <c r="I16" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
@@ -1644,6 +1744,9 @@
       <c r="D17" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="E17" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="F17" s="4" t="s">
         <v>33</v>
       </c>
@@ -1653,9 +1756,15 @@
       <c r="H17" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
+      <c r="I17" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
@@ -1670,6 +1779,9 @@
       <c r="D18" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="E18" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="F18" s="4" t="s">
         <v>33</v>
       </c>
@@ -1679,9 +1791,15 @@
       <c r="H18" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
+      <c r="I18" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
@@ -1696,6 +1814,9 @@
       <c r="D19" s="4" t="s">
         <v>47</v>
       </c>
+      <c r="E19" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="F19" s="4" t="s">
         <v>33</v>
       </c>
@@ -1705,9 +1826,15 @@
       <c r="H19" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
+      <c r="I19" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
@@ -1722,6 +1849,9 @@
       <c r="D20" s="4" t="s">
         <v>47</v>
       </c>
+      <c r="E20" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="F20" s="4" t="s">
         <v>33</v>
       </c>
@@ -1731,9 +1861,15 @@
       <c r="H20" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
+      <c r="I20" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
@@ -1748,6 +1884,9 @@
       <c r="D21" s="4" t="s">
         <v>51</v>
       </c>
+      <c r="E21" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="F21" s="4" t="s">
         <v>33</v>
       </c>
@@ -1757,9 +1896,15 @@
       <c r="H21" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
+      <c r="I21" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
@@ -1774,6 +1919,9 @@
       <c r="D22" s="4" t="s">
         <v>54</v>
       </c>
+      <c r="E22" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="F22" s="4" t="s">
         <v>33</v>
       </c>
@@ -1783,9 +1931,15 @@
       <c r="H22" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
+      <c r="I22" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
@@ -1800,6 +1954,9 @@
       <c r="D23" s="4" t="s">
         <v>56</v>
       </c>
+      <c r="E23" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="F23" s="4" t="s">
         <v>33</v>
       </c>
@@ -1809,9 +1966,15 @@
       <c r="H23" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
+      <c r="I23" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
@@ -1826,6 +1989,9 @@
       <c r="D24" s="4" t="s">
         <v>59</v>
       </c>
+      <c r="E24" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="F24" s="4" t="s">
         <v>33</v>
       </c>
@@ -1835,35 +2001,43 @@
       <c r="H24" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="5">
+      <c r="I24" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="22">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="E25" s="23"/>
+      <c r="F25" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G25" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="H25" s="7" t="s">
+      <c r="G25" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="H25" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="23"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
@@ -1878,6 +2052,9 @@
       <c r="D26" s="4" t="s">
         <v>94</v>
       </c>
+      <c r="E26" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="F26" s="4" t="s">
         <v>33</v>
       </c>
@@ -1887,9 +2064,15 @@
       <c r="H26" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
+      <c r="I26" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
@@ -1904,6 +2087,9 @@
       <c r="D27" s="4" t="s">
         <v>98</v>
       </c>
+      <c r="E27" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="F27" s="4" t="s">
         <v>33</v>
       </c>
@@ -1913,9 +2099,15 @@
       <c r="H27" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
+      <c r="I27" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
@@ -1930,6 +2122,9 @@
       <c r="D28" s="4" t="s">
         <v>104</v>
       </c>
+      <c r="E28" s="4" t="s">
+        <v>180</v>
+      </c>
       <c r="F28" s="4" t="s">
         <v>103</v>
       </c>
@@ -1939,37 +2134,43 @@
       <c r="H28" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="14">
+      <c r="I28" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="12">
         <v>28</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="C29" s="21" t="s">
+      <c r="C29" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="D29" s="21" t="s">
+      <c r="D29" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21" t="s">
+      <c r="E29" s="19"/>
+      <c r="F29" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="G29" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="H29" s="23" t="s">
+      <c r="G29" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="H29" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="20" t="s">
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="18" t="s">
         <v>169</v>
       </c>
     </row>
@@ -1986,6 +2187,9 @@
       <c r="D30" s="4" t="s">
         <v>112</v>
       </c>
+      <c r="E30" s="4" t="s">
+        <v>180</v>
+      </c>
       <c r="F30" s="4" t="s">
         <v>103</v>
       </c>
@@ -1995,67 +2199,73 @@
       <c r="H30" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="14">
+      <c r="I30" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="12">
         <v>30</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="C31" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="D31" s="21" t="s">
+      <c r="D31" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21" t="s">
+      <c r="E31" s="19"/>
+      <c r="F31" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="G31" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="H31" s="22" t="s">
+      <c r="G31" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="H31" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="20" t="s">
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="18" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="14">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="12">
         <v>31</v>
       </c>
-      <c r="B32" s="21" t="s">
+      <c r="B32" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="D32" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21" t="s">
+      <c r="E32" s="19"/>
+      <c r="F32" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="G32" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="H32" s="22" t="s">
+      <c r="G32" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="H32" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="20" t="s">
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="18" t="s">
         <v>169</v>
       </c>
     </row>
@@ -2072,6 +2282,9 @@
       <c r="D33" s="4" t="s">
         <v>123</v>
       </c>
+      <c r="E33" s="4" t="s">
+        <v>180</v>
+      </c>
       <c r="F33" s="4" t="s">
         <v>103</v>
       </c>
@@ -2081,9 +2294,15 @@
       <c r="H33" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
+      <c r="I33" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
@@ -2098,6 +2317,9 @@
       <c r="D34" s="4" t="s">
         <v>129</v>
       </c>
+      <c r="E34" s="4" t="s">
+        <v>180</v>
+      </c>
       <c r="F34" s="4" t="s">
         <v>103</v>
       </c>
@@ -2107,9 +2329,15 @@
       <c r="H34" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
+      <c r="I34" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
@@ -2124,6 +2352,9 @@
       <c r="D35" s="4" t="s">
         <v>131</v>
       </c>
+      <c r="E35" s="4" t="s">
+        <v>180</v>
+      </c>
       <c r="F35" s="4" t="s">
         <v>103</v>
       </c>
@@ -2133,9 +2364,15 @@
       <c r="H35" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
+      <c r="I35" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
@@ -2150,6 +2387,9 @@
       <c r="D36" s="4" t="s">
         <v>144</v>
       </c>
+      <c r="E36" s="4" t="s">
+        <v>181</v>
+      </c>
       <c r="F36" s="4" t="s">
         <v>139</v>
       </c>
@@ -2159,9 +2399,15 @@
       <c r="H36" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
+      <c r="I36" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
@@ -2176,6 +2422,9 @@
       <c r="D37" s="4" t="s">
         <v>148</v>
       </c>
+      <c r="E37" s="4" t="s">
+        <v>181</v>
+      </c>
       <c r="F37" s="4" t="s">
         <v>139</v>
       </c>
@@ -2185,9 +2434,15 @@
       <c r="H37" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
+      <c r="I37" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
@@ -2202,6 +2457,9 @@
       <c r="D38" s="4" t="s">
         <v>152</v>
       </c>
+      <c r="E38" s="4" t="s">
+        <v>181</v>
+      </c>
       <c r="F38" s="4" t="s">
         <v>139</v>
       </c>
@@ -2211,9 +2469,15 @@
       <c r="H38" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
+      <c r="I38" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
@@ -2228,6 +2492,9 @@
       <c r="D39" s="4" t="s">
         <v>156</v>
       </c>
+      <c r="E39" s="4" t="s">
+        <v>181</v>
+      </c>
       <c r="F39" s="4" t="s">
         <v>139</v>
       </c>
@@ -2237,9 +2504,15 @@
       <c r="H39" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
+      <c r="I39" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
@@ -2252,16 +2525,16 @@
       <c r="H41" s="7"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="26"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
@@ -2336,6 +2609,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L39" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="Y"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A43:H43"/>
   </mergeCells>

--- a/数据目录.xlsx
+++ b/数据目录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2-项目代码\aistockzml\data_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{A1FE921F-1306-4111-97C0-176202B0A382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C91DF9B-B9A4-408B-9378-A8753151D7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">源数据!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
